--- a/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleCommunicationType</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleCommunicationType</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,7 +404,7 @@
     <t>communicationProtocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleCommunicationProtocol}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleCommunicationProtocol}
 </t>
   </si>
   <si>
@@ -414,7 +414,7 @@
     <t>communicationTypeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleCommunicationTypeId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleCommunicationTypeId}
 </t>
   </si>
   <si>
@@ -424,7 +424,7 @@
     <t>isPaperCopy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleIsPaperCopy}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleIsPaperCopy}
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
+++ b/docs/StructureDefinition-DIPSPractitionerRoleCommunicationType.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
